--- a/Interview_Questions.xlsx
+++ b/Interview_Questions.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\Devops_Shack\raguraman-devsecops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21B569A-B384-4DBA-98BE-54BD1B958007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7131F9B7-68AA-4839-893C-FC384417CD09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="721" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Kubernetes (K8s)" sheetId="1" r:id="rId1"/>
-    <sheet name="Docker" sheetId="2" r:id="rId2"/>
-    <sheet name="Terraform" sheetId="3" r:id="rId3"/>
-    <sheet name="GitHub Actions" sheetId="4" r:id="rId4"/>
+    <sheet name="AWS" sheetId="5" r:id="rId1"/>
+    <sheet name="Kubernetes (K8s)" sheetId="1" r:id="rId2"/>
+    <sheet name="Docker" sheetId="2" r:id="rId3"/>
+    <sheet name="Terraform" sheetId="3" r:id="rId4"/>
+    <sheet name="GitHub Actions" sheetId="4" r:id="rId5"/>
+    <sheet name="Prometheus &amp; Grafana" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="54">
   <si>
     <t>Question</t>
   </si>
@@ -103,6 +105,93 @@
   </si>
   <si>
     <t>How to implement workflow concurrency?</t>
+  </si>
+  <si>
+    <t>Explain how you would design a highly available EC2 architecture across multiple AZs for a web application.</t>
+  </si>
+  <si>
+    <t>How would you migrate a running EC2 instance to another region with minimal downtime?</t>
+  </si>
+  <si>
+    <t>If your EC2 instance is not reachable via SSH, what troubleshooting steps would you perform?</t>
+  </si>
+  <si>
+    <t>Your web application experiences unpredictable traffic spikes. How would you configure auto scaling policies to handle this while optimizing costs?</t>
+  </si>
+  <si>
+    <t>Explain a scenario where scheduled scaling is more appropriate than dynamic scaling.</t>
+  </si>
+  <si>
+    <t>Your S3 bucket storing critical backups becomes unavailable. How would you recover?</t>
+  </si>
+  <si>
+    <t>You want to audit all IAM users and roles for compliance. How would you do this?</t>
+  </si>
+  <si>
+    <t>Your organization needs to grant cross-account access to a partner. How would you implement it?</t>
+  </si>
+  <si>
+    <t>How would you secure S3 data in transit and at rest for compliance?</t>
+  </si>
+  <si>
+    <t>How would you connect an on-premises network securely to your VPC?</t>
+  </si>
+  <si>
+    <t>How would you deploy Lambda functions across multiple environments securely?</t>
+  </si>
+  <si>
+    <t>How do you handle multi-cloud Docker deployments with compliance restrictions?</t>
+  </si>
+  <si>
+    <t>You need live-patching of Docker host kernel without downtime. How do you achieve it?</t>
+  </si>
+  <si>
+    <t>How do you troubleshoot container DNS resolution failures?</t>
+  </si>
+  <si>
+    <t>How do you enforce policy-as-code for Docker security?</t>
+  </si>
+  <si>
+    <t>Your Ingress controller crashes repeatedly under heavy load. How do you stabilize it?</t>
+  </si>
+  <si>
+    <t>An entire Kubernetes region goes down. How do you failover workloads?</t>
+  </si>
+  <si>
+    <t>All pods in one namespace suddenly fail readiness checks. What’s your step to troubleshoot?</t>
+  </si>
+  <si>
+    <t>Your cluster is hit by a massive traffic surge, and HPA cannot scale pods fast enough. How do you handle it?</t>
+  </si>
+  <si>
+    <t>A node hosting critical workloads crashes permanently. How do you ensure workloads recover automatically?</t>
+  </si>
+  <si>
+    <t>A Pod is stuck in ImagePullBackOff. How do you troubleshoot?</t>
+  </si>
+  <si>
+    <t>Your Terraform apply succeeded, but some resources are not behaving as expected. How do you debug?</t>
+  </si>
+  <si>
+    <t>How do you run Terraform safely in CI/CD pipelines?</t>
+  </si>
+  <si>
+    <t>Your Terraform state file is getting too large. How do you manage it?</t>
+  </si>
+  <si>
+    <t>A team needs to provision infra in 10 AWS regions simultaneously. How do you structure it?</t>
+  </si>
+  <si>
+    <t>You want faster Terraform runs in large projects. What optimizations would you apply?</t>
+  </si>
+  <si>
+    <t>A production deployment failed halfway, leaving some resources created and others not. How do you recover?</t>
+  </si>
+  <si>
+    <t>How do you implement Kubernetes cluster-level monitoring using Prometheus?</t>
+  </si>
+  <si>
+    <t>How can you integrate Prometheus with Alertmanager and Slack for real-time notifications?</t>
   </si>
 </sst>
 </file>
@@ -167,18 +256,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -461,11 +557,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82FB2531-C74D-41B9-9F92-D8AD03B4A94F}">
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="88.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="124.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -477,6 +573,147 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="6">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="6">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="6">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="6">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="6">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="6">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="6">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="6">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="6">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="6">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="6">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="6">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="6">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="6">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="93.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -554,6 +791,54 @@
       </c>
       <c r="B11" s="1" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -562,7 +847,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1868ADA2-4165-424B-ACE1-3CA12417077D}">
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -653,12 +938,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{371673D5-8D28-4E28-ABE2-ABC4CF01D091}">
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="74.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="94.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -705,44 +990,56 @@
       <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="4"/>
+      <c r="B6" s="1" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="1"/>
+      <c r="B7" s="1" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="1"/>
+      <c r="B9" s="1" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="1"/>
+      <c r="B10" s="1" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" s="1"/>
+      <c r="B11" s="1" t="s">
+        <v>51</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B022A23E-C0AF-4906-B328-B2BB95756EC9}">
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -829,4 +1126,89 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74957C40-4A1C-45F5-B2FF-FAA673A07585}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="78.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>